--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.7950735559039</v>
+        <v>4.516699452834383</v>
       </c>
       <c r="D2" t="n">
-        <v>26.89076922070268</v>
+        <v>4.369749998364186</v>
       </c>
       <c r="E2" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F2" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.27028918995636</v>
+        <v>10.44392199336791</v>
       </c>
       <c r="D3" t="n">
-        <v>63.55134183086928</v>
+        <v>10.32709304751626</v>
       </c>
       <c r="E3" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F3" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.47306152499281</v>
+        <v>4.626872497811332</v>
       </c>
       <c r="D4" t="n">
-        <v>27.93147307768345</v>
+        <v>4.53886437512356</v>
       </c>
       <c r="E4" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F4" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>74.9270717341311</v>
+        <v>12.17564915679631</v>
       </c>
       <c r="D5" t="n">
-        <v>74.32983308954272</v>
+        <v>12.07859787705069</v>
       </c>
       <c r="E5" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F5" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.81307713418827</v>
+        <v>4.032125034305594</v>
       </c>
       <c r="D6" t="n">
-        <v>24.69791507355064</v>
+        <v>4.013411199451978</v>
       </c>
       <c r="E6" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F6" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.17576266787876</v>
+        <v>5.066061433530299</v>
       </c>
       <c r="D7" t="n">
-        <v>31.84270697015922</v>
+        <v>5.174439882650873</v>
       </c>
       <c r="E7" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F7" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.87235804642544</v>
+        <v>5.504258182544135</v>
       </c>
       <c r="D8" t="n">
-        <v>34.78648170628176</v>
+        <v>5.652803277270786</v>
       </c>
       <c r="E8" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F8" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>66.35413306607282</v>
+        <v>10.78254662323683</v>
       </c>
       <c r="D9" t="n">
-        <v>67.10536977967192</v>
+        <v>10.90462258919669</v>
       </c>
       <c r="E9" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F9" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>78.78344884051181</v>
+        <v>12.80231043658317</v>
       </c>
       <c r="D10" t="n">
-        <v>78.92360171031162</v>
+        <v>12.82508527792564</v>
       </c>
       <c r="E10" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F10" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.75393632880922</v>
+        <v>10.0350146534315</v>
       </c>
       <c r="D11" t="n">
-        <v>61.62508990101331</v>
+        <v>10.01407710891466</v>
       </c>
       <c r="E11" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F11" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.12904650532992</v>
+        <v>3.270970057116112</v>
       </c>
       <c r="D12" t="n">
-        <v>20.03729527422832</v>
+        <v>3.256060482062103</v>
       </c>
       <c r="E12" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F12" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.97648519881493</v>
+        <v>6.008678844807426</v>
       </c>
       <c r="D13" t="n">
-        <v>36.84948708605388</v>
+        <v>5.988041651483757</v>
       </c>
       <c r="E13" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F13" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.15061615241423</v>
+        <v>2.624475124767312</v>
       </c>
       <c r="D14" t="n">
-        <v>16.28991188182114</v>
+        <v>2.647110680795935</v>
       </c>
       <c r="E14" t="n">
-        <v>21.34422018256383</v>
+        <v>3.468435779666623</v>
       </c>
       <c r="F14" t="n">
-        <v>21.32489705522772</v>
+        <v>3.465295771474505</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
